--- a/Fot_osv70_soc_taxi_2024.xlsx
+++ b/Fot_osv70_soc_taxi_2024.xlsx
@@ -473,8 +473,10 @@
           <t>osv70_год_из_имени_файла</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>2024</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -507,8 +509,10 @@
           <t>osv76_год_из_имени_файла</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>2024</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
     </row>
     <row r="8">
